--- a/tasks/finalpool/budget-variance-analysis-quarterly/groundtruth_workspace/variance_tracking.xlsx
+++ b/tasks/finalpool/budget-variance-analysis-quarterly/groundtruth_workspace/variance_tracking.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,46 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00366092"/>
-        <bgColor rgb="00366092"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -79,14 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -454,49 +415,42 @@
   </sheetPr>
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Monthly Budget Variance Tracking Dashboard</t>
-        </is>
-      </c>
-    </row>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Q1 FY2024 Monthly Variance Tracking</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>January</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>February</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>YTD Variance</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Q1 Variance</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
@@ -512,17 +466,17 @@
         <v>-2000</v>
       </c>
       <c r="C4" t="n">
-        <v>-5000</v>
+        <v>-2000</v>
       </c>
       <c r="D4" t="n">
-        <v>-8000</v>
+        <v>-2000</v>
       </c>
       <c r="E4" t="n">
-        <v>-15000</v>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Worsening</t>
+        <v>-6000</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
     </row>
@@ -533,18 +487,18 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15000</v>
+        <v>3500</v>
       </c>
       <c r="C5" t="n">
-        <v>22000</v>
+        <v>3500</v>
       </c>
       <c r="D5" t="n">
-        <v>21500</v>
+        <v>3500</v>
       </c>
       <c r="E5" t="n">
-        <v>58500</v>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+        <v>10500</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Increasing</t>
         </is>
@@ -557,20 +511,20 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="C6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E6" t="n">
         <v>15000</v>
       </c>
-      <c r="D6" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E6" t="n">
-        <v>45000</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Accelerating</t>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Increasing</t>
         </is>
       </c>
     </row>
@@ -581,56 +535,58 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Increasing</t>
-        </is>
-      </c>
-    </row>
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Variance Drivers by Department</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Supply costs, healthcare claims</t>
+          <t>Lower-than-planned salary spend</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Higher commissions from strong revenue</t>
+          <t>Higher commissions on strong Q1 revenue</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
@@ -642,21 +598,18 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Emergency equipment replacements</t>
+          <t>Emergency infrastructure replacements</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>